--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/35.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/35.xlsx
@@ -426,13 +426,13 @@
         <v>-7.098418609531137</v>
       </c>
       <c r="E2">
-        <v>-3.780906538243721</v>
+        <v>-5.405464889177408</v>
       </c>
       <c r="F2">
-        <v>-1.437371667441571</v>
+        <v>-1.374939273027378</v>
       </c>
       <c r="G2">
-        <v>-3.697797754395768</v>
+        <v>-4.071651041054585</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.263036258070384</v>
       </c>
       <c r="E3">
-        <v>-5.438776343977832</v>
+        <v>-6.25220348760562</v>
       </c>
       <c r="F3">
-        <v>-1.431344466218802</v>
+        <v>-1.554503646564824</v>
       </c>
       <c r="G3">
-        <v>-2.986162885274034</v>
+        <v>-2.994048604748578</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.430927799466708</v>
       </c>
       <c r="E4">
-        <v>-5.12247601996408</v>
+        <v>-6.973883747838006</v>
       </c>
       <c r="F4">
-        <v>-1.371577758106817</v>
+        <v>-1.711389805715828</v>
       </c>
       <c r="G4">
-        <v>-2.630338829622088</v>
+        <v>-2.925434237901643</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.718247661602683</v>
       </c>
       <c r="E5">
-        <v>-6.255015669964383</v>
+        <v>-7.245401992389906</v>
       </c>
       <c r="F5">
-        <v>-1.499503364488548</v>
+        <v>-1.538535208141057</v>
       </c>
       <c r="G5">
-        <v>-2.404751635485071</v>
+        <v>-3.347810190529557</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.108687472528119</v>
       </c>
       <c r="E6">
-        <v>-7.047272197606312</v>
+        <v>-9.098403743114531</v>
       </c>
       <c r="F6">
-        <v>-1.555066108031324</v>
+        <v>-1.882371464592868</v>
       </c>
       <c r="G6">
-        <v>-1.883089111588874</v>
+        <v>-2.719551410814368</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.627973686578443</v>
       </c>
       <c r="E7">
-        <v>-7.279727825368047</v>
+        <v>-9.433741771856528</v>
       </c>
       <c r="F7">
-        <v>-1.566608579421933</v>
+        <v>-1.453745177525306</v>
       </c>
       <c r="G7">
-        <v>-1.022923306302199</v>
+        <v>-2.411508458930723</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.268514242065871</v>
       </c>
       <c r="E8">
-        <v>-8.744254433344672</v>
+        <v>-11.16752691585523</v>
       </c>
       <c r="F8">
-        <v>-1.427220024920263</v>
+        <v>-1.511413631005999</v>
       </c>
       <c r="G8">
-        <v>-0.6370295655170528</v>
+        <v>-1.739378329729112</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.032141672655605</v>
       </c>
       <c r="E9">
-        <v>-9.781388192951374</v>
+        <v>-11.2331037479603</v>
       </c>
       <c r="F9">
-        <v>-1.366368155510611</v>
+        <v>-1.569858264743115</v>
       </c>
       <c r="G9">
-        <v>-0.7857558238688109</v>
+        <v>-1.439932864610955</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.903215666303251</v>
       </c>
       <c r="E10">
-        <v>-10.85239040966144</v>
+        <v>-12.34119416679319</v>
       </c>
       <c r="F10">
-        <v>-1.649165331519737</v>
+        <v>-1.281004894652122</v>
       </c>
       <c r="G10">
-        <v>-0.1404311818986784</v>
+        <v>-0.8621168672776401</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.862992545267866</v>
       </c>
       <c r="E11">
-        <v>-11.59910407420823</v>
+        <v>-13.14535605260128</v>
       </c>
       <c r="F11">
-        <v>-1.514289722628519</v>
+        <v>-1.446903691145585</v>
       </c>
       <c r="G11">
-        <v>0.02986990173251001</v>
+        <v>-1.198782795893824</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.89118507352429</v>
       </c>
       <c r="E12">
-        <v>-12.3383638705384</v>
+        <v>-13.21047098035758</v>
       </c>
       <c r="F12">
-        <v>-1.40925522105575</v>
+        <v>-1.602255713866604</v>
       </c>
       <c r="G12">
-        <v>0.588623777850701</v>
+        <v>-0.03336813915864821</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.959493276851186</v>
       </c>
       <c r="E13">
-        <v>-12.06775132078803</v>
+        <v>-14.51455375424244</v>
       </c>
       <c r="F13">
-        <v>-1.243950363990095</v>
+        <v>-1.278154482419089</v>
       </c>
       <c r="G13">
-        <v>1.22869458405001</v>
+        <v>-0.05308243784500813</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.050557599930019</v>
       </c>
       <c r="E14">
-        <v>-14.19862929357133</v>
+        <v>-15.90425185771632</v>
       </c>
       <c r="F14">
-        <v>-1.116725556431132</v>
+        <v>-1.264477308231466</v>
       </c>
       <c r="G14">
-        <v>1.386425526268586</v>
+        <v>0.3601266141846644</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.13744830055583</v>
       </c>
       <c r="E15">
-        <v>-14.84138730879803</v>
+        <v>-16.50536602596849</v>
       </c>
       <c r="F15">
-        <v>-0.942269724666751</v>
+        <v>-1.368023233581404</v>
       </c>
       <c r="G15">
-        <v>1.340475154183502</v>
+        <v>1.21443275386683</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.207815571583812</v>
       </c>
       <c r="E16">
-        <v>-16.06557421576557</v>
+        <v>-16.6127633155344</v>
       </c>
       <c r="F16">
-        <v>-0.712989224715487</v>
+        <v>-0.7013680584216128</v>
       </c>
       <c r="G16">
-        <v>1.745705791463531</v>
+        <v>1.614892895024769</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.246599340559107</v>
       </c>
       <c r="E17">
-        <v>-17.2758858783736</v>
+        <v>-18.31352229859516</v>
       </c>
       <c r="F17">
-        <v>-0.5167241359702002</v>
+        <v>-0.5014813473912865</v>
       </c>
       <c r="G17">
-        <v>2.630137895553064</v>
+        <v>1.742858722299757</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.255656214527368</v>
       </c>
       <c r="E18">
-        <v>-17.64907742134572</v>
+        <v>-18.46033089744982</v>
       </c>
       <c r="F18">
-        <v>-0.1284393414189739</v>
+        <v>-0.3770630485930091</v>
       </c>
       <c r="G18">
-        <v>1.995787712045615</v>
+        <v>2.069394381565771</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.236247712205447</v>
       </c>
       <c r="E19">
-        <v>-18.82210162897459</v>
+        <v>-19.33210290019244</v>
       </c>
       <c r="F19">
-        <v>-0.03596785987706229</v>
+        <v>-0.1220832783372933</v>
       </c>
       <c r="G19">
-        <v>1.704443151862055</v>
+        <v>2.55134360117287</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.202838469928309</v>
       </c>
       <c r="E20">
-        <v>-19.51866697236044</v>
+        <v>-19.52654651713378</v>
       </c>
       <c r="F20">
-        <v>0.04754979840798947</v>
+        <v>0.0702942821866555</v>
       </c>
       <c r="G20">
-        <v>2.675446021803529</v>
+        <v>1.886678752162316</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.165108243704389</v>
       </c>
       <c r="E21">
-        <v>-20.32537838903485</v>
+        <v>-21.514501321761</v>
       </c>
       <c r="F21">
-        <v>0.5324545384543473</v>
+        <v>0.7564956145829044</v>
       </c>
       <c r="G21">
-        <v>2.872483071209872</v>
+        <v>2.101437151840377</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.141025189550513</v>
       </c>
       <c r="E22">
-        <v>-20.83619931404808</v>
+        <v>-21.40010753985323</v>
       </c>
       <c r="F22">
-        <v>0.9841226931981805</v>
+        <v>1.093677595688026</v>
       </c>
       <c r="G22">
-        <v>2.56746926849466</v>
+        <v>1.782767348775672</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.140728340036173</v>
       </c>
       <c r="E23">
-        <v>-20.70727365904971</v>
+        <v>-21.57435416272038</v>
       </c>
       <c r="F23">
-        <v>1.316717175626599</v>
+        <v>1.138435943196089</v>
       </c>
       <c r="G23">
-        <v>2.512931341280707</v>
+        <v>1.541001518588236</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.176049987892561</v>
       </c>
       <c r="E24">
-        <v>-22.47337399356714</v>
+        <v>-22.74564396480431</v>
       </c>
       <c r="F24">
-        <v>1.545260428589371</v>
+        <v>1.160172303845548</v>
       </c>
       <c r="G24">
-        <v>2.12295569784564</v>
+        <v>1.228062269852009</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.251466871676087</v>
       </c>
       <c r="E25">
-        <v>-21.62735995098015</v>
+        <v>-22.48751188941909</v>
       </c>
       <c r="F25">
-        <v>1.693584582265039</v>
+        <v>1.559322793619296</v>
       </c>
       <c r="G25">
-        <v>1.420318891499644</v>
+        <v>0.8197263408561439</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.366508277166858</v>
       </c>
       <c r="E26">
-        <v>-22.03564263903771</v>
+        <v>-22.94543118107471</v>
       </c>
       <c r="F26">
-        <v>1.842200321266493</v>
+        <v>1.539667291885669</v>
       </c>
       <c r="G26">
-        <v>1.619537590416366</v>
+        <v>1.147990104893657</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.517934732393175</v>
       </c>
       <c r="E27">
-        <v>-21.71610445610847</v>
+        <v>-22.17589400752927</v>
       </c>
       <c r="F27">
-        <v>1.860439314741333</v>
+        <v>1.753500396509528</v>
       </c>
       <c r="G27">
-        <v>1.550996055571296</v>
+        <v>0.4187398229574607</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.692501131398578</v>
       </c>
       <c r="E28">
-        <v>-22.07931071389367</v>
+        <v>-22.30482419100165</v>
       </c>
       <c r="F28">
-        <v>2.185457548903747</v>
+        <v>1.970471356855191</v>
       </c>
       <c r="G28">
-        <v>0.8218881270932881</v>
+        <v>-0.1289137939675539</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.878203509940377</v>
       </c>
       <c r="E29">
-        <v>-21.54607384254247</v>
+        <v>-22.85142006067548</v>
       </c>
       <c r="F29">
-        <v>1.985391910514416</v>
+        <v>1.648410394320771</v>
       </c>
       <c r="G29">
-        <v>1.159173127725315</v>
+        <v>-0.1849182928554046</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.052570724679823</v>
       </c>
       <c r="E30">
-        <v>-21.75699204792373</v>
+        <v>-21.73045066176477</v>
       </c>
       <c r="F30">
-        <v>2.059819064921146</v>
+        <v>1.89066147106507</v>
       </c>
       <c r="G30">
-        <v>0.04562478795390159</v>
+        <v>-0.5179095159229969</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.198347467845176</v>
       </c>
       <c r="E31">
-        <v>-21.29776855575389</v>
+        <v>-20.28096764444163</v>
       </c>
       <c r="F31">
-        <v>1.957018670233727</v>
+        <v>2.151298990681906</v>
       </c>
       <c r="G31">
-        <v>0.1348108847818674</v>
+        <v>-0.9058326211237161</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.291824795618562</v>
       </c>
       <c r="E32">
-        <v>-20.98180333881671</v>
+        <v>-20.77802653694555</v>
       </c>
       <c r="F32">
-        <v>2.237729188755201</v>
+        <v>1.633408660656072</v>
       </c>
       <c r="G32">
-        <v>-0.3214220170761735</v>
+        <v>-0.9935819411876382</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.318496547812923</v>
       </c>
       <c r="E33">
-        <v>-20.44550521903632</v>
+        <v>-21.49785012283479</v>
       </c>
       <c r="F33">
-        <v>1.622101445607859</v>
+        <v>1.410171929275633</v>
       </c>
       <c r="G33">
-        <v>-0.4477358821270656</v>
+        <v>-1.396078067852229</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.264373001490391</v>
       </c>
       <c r="E34">
-        <v>-19.9570096708809</v>
+        <v>-20.56618905134074</v>
       </c>
       <c r="F34">
-        <v>1.767352356219141</v>
+        <v>1.534198410292387</v>
       </c>
       <c r="G34">
-        <v>0.2782766862717235</v>
+        <v>-1.554044058804093</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.128919731465267</v>
       </c>
       <c r="E35">
-        <v>-19.17908576347325</v>
+        <v>-20.08099023226291</v>
       </c>
       <c r="F35">
-        <v>1.816090180730253</v>
+        <v>1.52989421326744</v>
       </c>
       <c r="G35">
-        <v>-0.3001120354398848</v>
+        <v>-1.339967631507122</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.916280722800928</v>
       </c>
       <c r="E36">
-        <v>-19.31392560552565</v>
+        <v>-19.44444528337472</v>
       </c>
       <c r="F36">
-        <v>1.637126373559836</v>
+        <v>1.18595441089028</v>
       </c>
       <c r="G36">
-        <v>-0.9772013618593244</v>
+        <v>-1.693494168554813</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.64195471109882</v>
       </c>
       <c r="E37">
-        <v>-18.1790583198854</v>
+        <v>-19.49463888927574</v>
       </c>
       <c r="F37">
-        <v>1.683069286453903</v>
+        <v>1.510720821362243</v>
       </c>
       <c r="G37">
-        <v>-0.576347265782212</v>
+        <v>-1.795780094081675</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.325202701073222</v>
       </c>
       <c r="E38">
-        <v>-18.10617253073195</v>
+        <v>-19.05774530243773</v>
       </c>
       <c r="F38">
-        <v>1.400085727779147</v>
+        <v>1.46878223649331</v>
       </c>
       <c r="G38">
-        <v>-0.1284635597742131</v>
+        <v>-0.8571245646044191</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.989490640504368</v>
       </c>
       <c r="E39">
-        <v>-18.145167220412</v>
+        <v>-17.86118208691698</v>
       </c>
       <c r="F39">
-        <v>1.253242695019684</v>
+        <v>1.049492478422701</v>
       </c>
       <c r="G39">
-        <v>0.05156721719689337</v>
+        <v>-1.015679832662273</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.660575322491892</v>
       </c>
       <c r="E40">
-        <v>-16.67083193773476</v>
+        <v>-17.74972275616619</v>
       </c>
       <c r="F40">
-        <v>1.221609000641576</v>
+        <v>1.036778695524534</v>
       </c>
       <c r="G40">
-        <v>0.5901598709809228</v>
+        <v>-0.707372037135487</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.358753164382918</v>
       </c>
       <c r="E41">
-        <v>-16.32296814988754</v>
+        <v>-17.10490428526599</v>
       </c>
       <c r="F41">
-        <v>1.269390889169858</v>
+        <v>1.060523018758379</v>
       </c>
       <c r="G41">
-        <v>0.6938726416352106</v>
+        <v>-0.05795225033327604</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.105546349239167</v>
       </c>
       <c r="E42">
-        <v>-16.04572138571594</v>
+        <v>-17.36741086654263</v>
       </c>
       <c r="F42">
-        <v>0.8799737163790042</v>
+        <v>0.5649787277904642</v>
       </c>
       <c r="G42">
-        <v>1.022785272598421</v>
+        <v>0.0007304798958450186</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.910315907872366</v>
       </c>
       <c r="E43">
-        <v>-14.95333571474165</v>
+        <v>-17.00549069537561</v>
       </c>
       <c r="F43">
-        <v>1.031097751876135</v>
+        <v>0.971238266615037</v>
       </c>
       <c r="G43">
-        <v>1.256595861854988</v>
+        <v>0.2781641277233883</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.78482614903735</v>
       </c>
       <c r="E44">
-        <v>-15.29618195338837</v>
+        <v>-15.63070032833498</v>
       </c>
       <c r="F44">
-        <v>0.8840492840007779</v>
+        <v>0.7069940353264115</v>
       </c>
       <c r="G44">
-        <v>0.9564187661726513</v>
+        <v>0.7010432832732719</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.726750519063671</v>
       </c>
       <c r="E45">
-        <v>-14.66517985668557</v>
+        <v>-14.34175171458375</v>
       </c>
       <c r="F45">
-        <v>0.7640917436665758</v>
+        <v>0.6974595265201892</v>
       </c>
       <c r="G45">
-        <v>1.294620787919057</v>
+        <v>0.7955593584194643</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.737121647688845</v>
       </c>
       <c r="E46">
-        <v>-13.74373049407881</v>
+        <v>-13.5533806176404</v>
       </c>
       <c r="F46">
-        <v>0.6481733227884242</v>
+        <v>0.3821646689318358</v>
       </c>
       <c r="G46">
-        <v>1.289979403072998</v>
+        <v>0.5768647200952097</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.804032488516887</v>
       </c>
       <c r="E47">
-        <v>-12.10195488496796</v>
+        <v>-13.94257125928161</v>
       </c>
       <c r="F47">
-        <v>0.3141689590404411</v>
+        <v>0.2659414088494539</v>
       </c>
       <c r="G47">
-        <v>1.794595927987487</v>
+        <v>-0.1196210926388197</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.921294433696289</v>
       </c>
       <c r="E48">
-        <v>-11.25240410418099</v>
+        <v>-13.04402691820565</v>
       </c>
       <c r="F48">
-        <v>0.4043789975727101</v>
+        <v>0.0220335972995563</v>
       </c>
       <c r="G48">
-        <v>1.53916747635948</v>
+        <v>0.3589844759736158</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.07348714994507</v>
       </c>
       <c r="E49">
-        <v>-11.75388731579041</v>
+        <v>-12.49231840137717</v>
       </c>
       <c r="F49">
-        <v>0.2869620600628942</v>
+        <v>0.4205213931510641</v>
       </c>
       <c r="G49">
-        <v>1.559494225970605</v>
+        <v>1.132639105228057</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.254739142456824</v>
       </c>
       <c r="E50">
-        <v>-11.46590806822062</v>
+        <v>-12.97839121593848</v>
       </c>
       <c r="F50">
-        <v>0.4100218363205803</v>
+        <v>0.1446899586320791</v>
       </c>
       <c r="G50">
-        <v>2.493577892058128</v>
+        <v>0.8287839934515899</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.45321148492075</v>
       </c>
       <c r="E51">
-        <v>-11.09927375561162</v>
+        <v>-11.72941997072696</v>
       </c>
       <c r="F51">
-        <v>0.2174628633354184</v>
+        <v>0.05361261942907905</v>
       </c>
       <c r="G51">
-        <v>1.59245070681405</v>
+        <v>0.5071578732203156</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.667212402415366</v>
       </c>
       <c r="E52">
-        <v>-10.03461140251228</v>
+        <v>-10.96868615065243</v>
       </c>
       <c r="F52">
-        <v>0.3693581088845554</v>
+        <v>-0.273363875273553</v>
       </c>
       <c r="G52">
-        <v>1.679931872689291</v>
+        <v>0.4778694768343834</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.891946591309861</v>
       </c>
       <c r="E53">
-        <v>-10.27041357256569</v>
+        <v>-10.60780300003316</v>
       </c>
       <c r="F53">
-        <v>0.4138381249452777</v>
+        <v>0.1244305770618116</v>
       </c>
       <c r="G53">
-        <v>1.712530814614494</v>
+        <v>0.9452953331607001</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.129289646426201</v>
       </c>
       <c r="E54">
-        <v>-9.007847848383147</v>
+        <v>-9.909467023310315</v>
       </c>
       <c r="F54">
-        <v>0.1595417577968714</v>
+        <v>-0.02070601884788419</v>
       </c>
       <c r="G54">
-        <v>0.8522656929616405</v>
+        <v>0.5310136643763037</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.380520093837328</v>
       </c>
       <c r="E55">
-        <v>-8.612652450207763</v>
+        <v>-9.810578736404818</v>
       </c>
       <c r="F55">
-        <v>-0.05084616679874421</v>
+        <v>0.122978449004704</v>
       </c>
       <c r="G55">
-        <v>1.350267747888666</v>
+        <v>-0.2119224128192397</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.645982646421354</v>
       </c>
       <c r="E56">
-        <v>-8.636970355628952</v>
+        <v>-8.833986145806659</v>
       </c>
       <c r="F56">
-        <v>-0.1140911896350837</v>
+        <v>-0.03815889165746698</v>
       </c>
       <c r="G56">
-        <v>0.7553693355727121</v>
+        <v>-0.09512967673929147</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.926717939491326</v>
       </c>
       <c r="E57">
-        <v>-8.553189058013043</v>
+        <v>-8.822886856013859</v>
       </c>
       <c r="F57">
-        <v>0.1878719229726145</v>
+        <v>-0.2270332864349767</v>
       </c>
       <c r="G57">
-        <v>0.7857237276222896</v>
+        <v>-0.3949690967766222</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.216914641337983</v>
       </c>
       <c r="E58">
-        <v>-7.147451099603995</v>
+        <v>-8.861437755241157</v>
       </c>
       <c r="F58">
-        <v>0.05409969946192516</v>
+        <v>-0.1921184287743803</v>
       </c>
       <c r="G58">
-        <v>-0.4596074984308921</v>
+        <v>-0.5253483117497393</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.514449105047079</v>
       </c>
       <c r="E59">
-        <v>-6.663619879676479</v>
+        <v>-8.012240195426781</v>
       </c>
       <c r="F59">
-        <v>-0.182145713612077</v>
+        <v>-0.4429770712011686</v>
       </c>
       <c r="G59">
-        <v>0.6770418281135558</v>
+        <v>-0.8671522070428715</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.808037234985637</v>
       </c>
       <c r="E60">
-        <v>-6.407448633536575</v>
+        <v>-8.201371912357134</v>
       </c>
       <c r="F60">
-        <v>-0.1866586592225287</v>
+        <v>-0.299529516425781</v>
       </c>
       <c r="G60">
-        <v>-0.4814438568079248</v>
+        <v>-1.220675433545024</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.093710716040953</v>
       </c>
       <c r="E61">
-        <v>-6.765084868292341</v>
+        <v>-8.086928317235287</v>
       </c>
       <c r="F61">
-        <v>-0.2950281679589685</v>
+        <v>-0.3523520206000971</v>
       </c>
       <c r="G61">
-        <v>-0.589056450107474</v>
+        <v>-0.9653529193742728</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.356920097762566</v>
       </c>
       <c r="E62">
-        <v>-6.44932796115951</v>
+        <v>-7.721503107186328</v>
       </c>
       <c r="F62">
-        <v>-0.4751334654104426</v>
+        <v>-0.3193415795985368</v>
       </c>
       <c r="G62">
-        <v>-0.83218291451155</v>
+        <v>-1.908232704959639</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.592688577228161</v>
       </c>
       <c r="E63">
-        <v>-5.625634766956334</v>
+        <v>-6.584788204150954</v>
       </c>
       <c r="F63">
-        <v>-0.4570692574575937</v>
+        <v>-0.477433013320614</v>
       </c>
       <c r="G63">
-        <v>-1.009230889951773</v>
+        <v>-2.001388145889191</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.786136008858409</v>
       </c>
       <c r="E64">
-        <v>-5.650881009549096</v>
+        <v>-6.340993277474012</v>
       </c>
       <c r="F64">
-        <v>-0.3017222049409913</v>
+        <v>-0.4207726829691278</v>
       </c>
       <c r="G64">
-        <v>-2.066708519924551</v>
+        <v>-2.151034735900866</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.934508721639859</v>
       </c>
       <c r="E65">
-        <v>-5.657053319621551</v>
+        <v>-7.044233591547165</v>
       </c>
       <c r="F65">
-        <v>-0.5925007008760905</v>
+        <v>-0.8768195878041593</v>
       </c>
       <c r="G65">
-        <v>-1.586815149097339</v>
+        <v>-1.984640096006018</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.028999520266463</v>
       </c>
       <c r="E66">
-        <v>-4.856690823505891</v>
+        <v>-6.426128588818215</v>
       </c>
       <c r="F66">
-        <v>-0.6064876844723602</v>
+        <v>-0.6885913196008332</v>
       </c>
       <c r="G66">
-        <v>-1.384352115552131</v>
+        <v>-2.215544026279105</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.071498165388369</v>
       </c>
       <c r="E67">
-        <v>-6.154954508290898</v>
+        <v>-6.310833640582928</v>
       </c>
       <c r="F67">
-        <v>-0.3793584546661665</v>
+        <v>-0.8697188224273619</v>
       </c>
       <c r="G67">
-        <v>-1.872028578942169</v>
+        <v>-2.007731151142434</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.063618325956209</v>
       </c>
       <c r="E68">
-        <v>-4.307590707705822</v>
+        <v>-6.155375656373612</v>
       </c>
       <c r="F68">
-        <v>-0.7372910392114161</v>
+        <v>-0.8600567450411084</v>
       </c>
       <c r="G68">
-        <v>-1.593230986352446</v>
+        <v>-1.892947916204824</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.011813903892285</v>
       </c>
       <c r="E69">
-        <v>-4.354374372679064</v>
+        <v>-6.48101369379118</v>
       </c>
       <c r="F69">
-        <v>-0.7254685796386616</v>
+        <v>-0.9868549433876288</v>
       </c>
       <c r="G69">
-        <v>-1.424019072203678</v>
+        <v>-2.371848123370254</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.928151672469283</v>
       </c>
       <c r="E70">
-        <v>-5.2310008995579</v>
+        <v>-6.065073356186657</v>
       </c>
       <c r="F70">
-        <v>-1.220300474640169</v>
+        <v>-1.036464210406486</v>
       </c>
       <c r="G70">
-        <v>-1.844647056786857</v>
+        <v>-2.519591149696849</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.820582002964982</v>
       </c>
       <c r="E71">
-        <v>-4.755429616220375</v>
+        <v>-5.983859703333097</v>
       </c>
       <c r="F71">
-        <v>-0.6975815910234162</v>
+        <v>-1.02635481462272</v>
       </c>
       <c r="G71">
-        <v>-1.695076609322585</v>
+        <v>-2.412792950599961</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.706320469776209</v>
       </c>
       <c r="E72">
-        <v>-5.067781110899437</v>
+        <v>-5.945449186800038</v>
       </c>
       <c r="F72">
-        <v>-0.857129294639615</v>
+        <v>-1.05642372297694</v>
       </c>
       <c r="G72">
-        <v>-1.644233250930458</v>
+        <v>-2.177651522036606</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.591489992130205</v>
       </c>
       <c r="E73">
-        <v>-5.716638980614477</v>
+        <v>-6.54442138684658</v>
       </c>
       <c r="F73">
-        <v>-1.321326506350791</v>
+        <v>-1.348647720029924</v>
       </c>
       <c r="G73">
-        <v>-1.954706143239928</v>
+        <v>-2.150028330056928</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.491564093135132</v>
       </c>
       <c r="E74">
-        <v>-5.839591578396735</v>
+        <v>-7.656940653258972</v>
       </c>
       <c r="F74">
-        <v>-1.150155979705912</v>
+        <v>-1.299691206524473</v>
       </c>
       <c r="G74">
-        <v>-1.838986023914703</v>
+        <v>-2.274746512157891</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.406696846087311</v>
       </c>
       <c r="E75">
-        <v>-6.588773261277703</v>
+        <v>-6.921928565548004</v>
       </c>
       <c r="F75">
-        <v>-0.8243391993671993</v>
+        <v>-1.35900893950414</v>
       </c>
       <c r="G75">
-        <v>-1.91672425426787</v>
+        <v>-1.942400845470457</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.345205137964632</v>
       </c>
       <c r="E76">
-        <v>-6.704883334834371</v>
+        <v>-7.72465039662166</v>
       </c>
       <c r="F76">
-        <v>-1.28130310691713</v>
+        <v>-1.583988555900069</v>
       </c>
       <c r="G76">
-        <v>-1.477027527378488</v>
+        <v>-2.037794215184556</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.299196558690098</v>
       </c>
       <c r="E77">
-        <v>-7.009396041006157</v>
+        <v>-7.718627526191458</v>
       </c>
       <c r="F77">
-        <v>-1.1876130969257</v>
+        <v>-1.508514345096201</v>
       </c>
       <c r="G77">
-        <v>-1.201139904317785</v>
+        <v>-1.964022018387437</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.268810481813393</v>
       </c>
       <c r="E78">
-        <v>-7.18491969354346</v>
+        <v>-8.546373704631499</v>
       </c>
       <c r="F78">
-        <v>-1.348631981049271</v>
+        <v>-1.579644597239789</v>
       </c>
       <c r="G78">
-        <v>-0.9245471350572161</v>
+        <v>-1.913052859264818</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.241550954982729</v>
       </c>
       <c r="E79">
-        <v>-7.282775488375209</v>
+        <v>-9.399456695144456</v>
       </c>
       <c r="F79">
-        <v>-1.246370853541075</v>
+        <v>-1.69005023305231</v>
       </c>
       <c r="G79">
-        <v>-0.8048444294482485</v>
+        <v>-1.434831313934938</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.213995905934023</v>
       </c>
       <c r="E80">
-        <v>-8.292856144260091</v>
+        <v>-9.553447453775288</v>
       </c>
       <c r="F80">
-        <v>-1.730660944974555</v>
+        <v>-1.539113408588212</v>
       </c>
       <c r="G80">
-        <v>-0.8012723508113749</v>
+        <v>-1.751849154775547</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.177577036774046</v>
       </c>
       <c r="E81">
-        <v>-8.80908406723848</v>
+        <v>-9.784983801313464</v>
       </c>
       <c r="F81">
-        <v>-1.504322806038035</v>
+        <v>-1.960104633304171</v>
       </c>
       <c r="G81">
-        <v>-0.3829882324699997</v>
+        <v>-0.9392161623417268</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.13014787206753</v>
       </c>
       <c r="E82">
-        <v>-9.891158402897304</v>
+        <v>-10.42730255456143</v>
       </c>
       <c r="F82">
-        <v>-1.747127232207404</v>
+        <v>-1.577737695478544</v>
       </c>
       <c r="G82">
-        <v>-0.9538487736253054</v>
+        <v>-1.4459050887638</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.072414579049052</v>
       </c>
       <c r="E83">
-        <v>-10.98244818316174</v>
+        <v>-10.94779630005504</v>
       </c>
       <c r="F83">
-        <v>-2.02513395952614</v>
+        <v>-2.029347036136778</v>
       </c>
       <c r="G83">
-        <v>-0.3572421198110877</v>
+        <v>-1.221337542652878</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.004593817455782</v>
       </c>
       <c r="E84">
-        <v>-12.44217008021622</v>
+        <v>-12.85551107374034</v>
       </c>
       <c r="F84">
-        <v>-1.878097088794422</v>
+        <v>-2.171915693097796</v>
       </c>
       <c r="G84">
-        <v>-0.3221437160037346</v>
+        <v>-1.027448822054382</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.934515537294254</v>
       </c>
       <c r="E85">
-        <v>-12.30346292136128</v>
+        <v>-13.02397483529969</v>
       </c>
       <c r="F85">
-        <v>-1.665036022589973</v>
+        <v>-2.036865298684587</v>
       </c>
       <c r="G85">
-        <v>-0.09689088696618374</v>
+        <v>-0.6703369641876602</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.861879798695635</v>
       </c>
       <c r="E86">
-        <v>-13.91691292555415</v>
+        <v>-15.53243244236853</v>
       </c>
       <c r="F86">
-        <v>-1.924449215185472</v>
+        <v>-2.359327191041962</v>
       </c>
       <c r="G86">
-        <v>-0.03834057855863353</v>
+        <v>-0.9535210296169175</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.796583330860712</v>
       </c>
       <c r="E87">
-        <v>-15.56513255317792</v>
+        <v>-15.73805686163482</v>
       </c>
       <c r="F87">
-        <v>-2.238244727774758</v>
+        <v>-2.566019768653689</v>
       </c>
       <c r="G87">
-        <v>0.02494049942453521</v>
+        <v>-0.6067513160148785</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.73701291604127</v>
       </c>
       <c r="E88">
-        <v>-16.33635884752822</v>
+        <v>-17.62898911064769</v>
       </c>
       <c r="F88">
-        <v>-2.185950722003428</v>
+        <v>-2.353869078224916</v>
       </c>
       <c r="G88">
-        <v>0.2241525772501789</v>
+        <v>-0.4800534276814309</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.692064242292804</v>
       </c>
       <c r="E89">
-        <v>-17.8345682451739</v>
+        <v>-18.70198838439514</v>
       </c>
       <c r="F89">
-        <v>-2.313643557144972</v>
+        <v>-2.867910813297343</v>
       </c>
       <c r="G89">
-        <v>0.9863427873021235</v>
+        <v>-0.1086830501770677</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.657578934818821</v>
       </c>
       <c r="E90">
-        <v>-19.14922953434068</v>
+        <v>-20.28418286098707</v>
       </c>
       <c r="F90">
-        <v>-2.716629387993681</v>
+        <v>-2.666558720331465</v>
       </c>
       <c r="G90">
-        <v>0.2365836757501422</v>
+        <v>-0.9362995717216288</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.640191701966151</v>
       </c>
       <c r="E91">
-        <v>-21.08897420468223</v>
+        <v>-22.1615070456069</v>
       </c>
       <c r="F91">
-        <v>-2.429291101882408</v>
+        <v>-3.000234222220536</v>
       </c>
       <c r="G91">
-        <v>-0.1152875885279137</v>
+        <v>-0.7699910060108015</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.634188698424536</v>
       </c>
       <c r="E92">
-        <v>-22.37899153829927</v>
+        <v>-23.41728458725194</v>
       </c>
       <c r="F92">
-        <v>-2.877065101465681</v>
+        <v>-3.059158480683874</v>
       </c>
       <c r="G92">
-        <v>-0.3500218199899373</v>
+        <v>-1.114529411919372</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.645575999902111</v>
       </c>
       <c r="E93">
-        <v>-24.58750114099606</v>
+        <v>-25.50243855797979</v>
       </c>
       <c r="F93">
-        <v>-2.851970539365273</v>
+        <v>-3.405228015653631</v>
       </c>
       <c r="G93">
-        <v>-0.2275647404922961</v>
+        <v>-0.7883744653903744</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.670078880952018</v>
       </c>
       <c r="E94">
-        <v>-26.50664125460271</v>
+        <v>-27.23911739686939</v>
       </c>
       <c r="F94">
-        <v>-2.876167151201046</v>
+        <v>-3.554156877533343</v>
       </c>
       <c r="G94">
-        <v>-1.253426660565034</v>
+        <v>-1.612809552671696</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.713409211493345</v>
       </c>
       <c r="E95">
-        <v>-28.85348668128581</v>
+        <v>-29.65165286750775</v>
       </c>
       <c r="F95">
-        <v>-3.293450603422075</v>
+        <v>-3.632501381387912</v>
       </c>
       <c r="G95">
-        <v>-0.7244842470279798</v>
+        <v>-2.352656890879099</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.777843975754457</v>
       </c>
       <c r="E96">
-        <v>-31.44891816014597</v>
+        <v>-31.46701620651763</v>
       </c>
       <c r="F96">
-        <v>-3.500829069243319</v>
+        <v>-3.393335144851639</v>
       </c>
       <c r="G96">
-        <v>-1.576797438295504</v>
+        <v>-2.201722498652647</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.86341032505138</v>
       </c>
       <c r="E97">
-        <v>-34.36582148033664</v>
+        <v>-33.95086382159178</v>
       </c>
       <c r="F97">
-        <v>-3.729446046904941</v>
+        <v>-3.739758392702392</v>
       </c>
       <c r="G97">
-        <v>-1.11512531011644</v>
+        <v>-2.81284258411103</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.979867882218484</v>
       </c>
       <c r="E98">
-        <v>-36.77103893697861</v>
+        <v>-36.67129703272267</v>
       </c>
       <c r="F98">
-        <v>-3.448517667756531</v>
+        <v>-3.809167297382963</v>
       </c>
       <c r="G98">
-        <v>-1.752415258062762</v>
+        <v>-3.419821177099784</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.116972400896639</v>
       </c>
       <c r="E99">
-        <v>-38.58095905023126</v>
+        <v>-39.22673302914708</v>
       </c>
       <c r="F99">
-        <v>-3.731456494591535</v>
+        <v>-3.994252739660067</v>
       </c>
       <c r="G99">
-        <v>-2.872505235819775</v>
+        <v>-3.684198033320442</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.296321607289988</v>
       </c>
       <c r="E100">
-        <v>-41.13578596690165</v>
+        <v>-41.58937603740594</v>
       </c>
       <c r="F100">
-        <v>-3.876587291929412</v>
+        <v>-3.916760625862979</v>
       </c>
       <c r="G100">
-        <v>-3.043259864189844</v>
+        <v>-3.507759198259445</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.489645738313773</v>
       </c>
       <c r="E101">
-        <v>-42.86061831778718</v>
+        <v>-43.41841310368198</v>
       </c>
       <c r="F101">
-        <v>-4.226034909167786</v>
+        <v>-4.289729735503846</v>
       </c>
       <c r="G101">
-        <v>-3.268155154309154</v>
+        <v>-4.451595731505661</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.744943163245879</v>
       </c>
       <c r="E102">
-        <v>-46.40944980761521</v>
+        <v>-46.3374742417373</v>
       </c>
       <c r="F102">
-        <v>-3.844957739388318</v>
+        <v>-4.349510525861677</v>
       </c>
       <c r="G102">
-        <v>-3.495794886680519</v>
+        <v>-4.398822325064138</v>
       </c>
     </row>
   </sheetData>
